--- a/consent_forms/031_wearable_health_device_tracking_consent_form--consent_forms.xlsx
+++ b/consent_forms/031_wearable_health_device_tracking_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -987,8 +987,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'participant_e-signature',_'label':_'e-signature'}</t>
+          <t>e-signature</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'Participant E-Signature', 'label': 'E-Signature'}</t>
+          <t>E-Signature</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'participant_e-signature_2',_'label':_'e-signature_2'}</t>
+          <t>e-signature_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'Participant E-Signature 2', 'label': 'E-Signature 2'}</t>
+          <t>E-Signature 2</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'participant_consent',_'label':_'i_give_permission'}</t>
+          <t>i_give_permission</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'participant_consent', 'label': 'I give permission'}</t>
+          <t>I give permission</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'participant_consent_2',_'label':_'participant_consent_2'}</t>
+          <t>participant_consent_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'participant_consent_2', 'label': 'Participant Consent 2'}</t>
+          <t>Participant Consent 2</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'signature_1',_'label':_'signature_1'}</t>
+          <t>signature_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'signature_1', 'label': 'Signature 1'}</t>
+          <t>Signature 1</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'signature_2',_'label':_'signature_2'}</t>
+          <t>signature_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'signature_2', 'label': 'Signature 2'}</t>
+          <t>Signature 2</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'signature_3',_'label':_'signature_3'}</t>
+          <t>signature_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'signature_3', 'label': 'Signature 3'}</t>
+          <t>Signature 3</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'participant_consent_form_1',_'label':_'consent_form_1'}</t>
+          <t>consent_form_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'participant_consent_form_1', 'label': 'Consent Form 1'}</t>
+          <t>Consent Form 1</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'participant_consent_form_2',_'label':_'consent_form_2'}</t>
+          <t>consent_form_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'participant_consent_form_2', 'label': 'Consent Form 2'}</t>
+          <t>Consent Form 2</t>
         </is>
       </c>
     </row>
